--- a/product_selector_out/STM32L5 series.xlsx
+++ b/product_selector_out/STM32L5 series.xlsx
@@ -1234,7 +1234,7 @@
       </c>
       <c r="AW12" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX12" s="4" t="inlineStr">
@@ -1561,7 +1561,7 @@
       </c>
       <c r="AW13" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX13" s="4" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="AW14" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX14" s="4" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="AW15" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX15" s="4" t="inlineStr">
@@ -2542,7 +2542,7 @@
       </c>
       <c r="AW16" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX16" s="4" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="AW17" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX17" s="4" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="AW18" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX18" s="4" t="inlineStr">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="AW19" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX19" s="4" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="AW20" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX20" s="4" t="inlineStr">
@@ -4177,7 +4177,7 @@
       </c>
       <c r="AW21" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX21" s="4" t="inlineStr">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="AW22" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX22" s="4" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="AW23" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX23" s="4" t="inlineStr">
@@ -5158,7 +5158,7 @@
       </c>
       <c r="AW24" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX24" s="4" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="AW25" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX25" s="4" t="inlineStr">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="AW26" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX26" s="4" t="inlineStr">
@@ -6139,7 +6139,7 @@
       </c>
       <c r="AW27" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX27" s="4" t="inlineStr">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="AW28" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX28" s="4" t="inlineStr">
@@ -7385,9 +7385,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW12" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW12" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX12" s="7" t="inlineStr">
@@ -7712,9 +7712,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW13" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX13" s="7" t="inlineStr">
@@ -8039,9 +8039,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW14" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX14" s="7" t="inlineStr">
@@ -8366,9 +8366,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW15" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW15" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX15" s="7" t="inlineStr">
@@ -8693,9 +8693,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW16" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW16" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX16" s="7" t="inlineStr">
@@ -9020,9 +9020,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW17" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW17" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX17" s="7" t="inlineStr">
@@ -9347,9 +9347,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW18" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW18" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX18" s="7" t="inlineStr">
@@ -9674,9 +9674,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW19" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW19" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX19" s="7" t="inlineStr">
@@ -10001,9 +10001,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW20" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW20" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX20" s="7" t="inlineStr">
@@ -10328,9 +10328,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW21" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW21" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX21" s="7" t="inlineStr">
@@ -10655,9 +10655,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW22" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW22" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX22" s="7" t="inlineStr">
@@ -10982,9 +10982,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW23" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW23" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX23" s="7" t="inlineStr">
@@ -11309,9 +11309,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW24" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW24" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX24" s="7" t="inlineStr">
@@ -11636,9 +11636,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW25" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW25" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX25" s="7" t="inlineStr">
@@ -11963,9 +11963,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW26" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW26" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX26" s="7" t="inlineStr">
@@ -12290,9 +12290,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW27" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW27" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX27" s="7" t="inlineStr">
@@ -12617,9 +12617,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW28" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW28" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX28" s="7" t="inlineStr">
@@ -12718,7 +12718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -12796,12 +12796,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>STM32L552QE</t>
+          <t>STM32L562RE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -12811,7 +12811,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Table 16. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 27. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -12823,7 +12823,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -12840,12 +12840,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STM32L552ZC</t>
+          <t>STM32L552QE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -12862,12 +12862,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STM32L552ZC</t>
+          <t>STM32L552QE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -12877,14 +12877,14 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Table 16. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 27. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STM32L552RE</t>
+          <t>STM32L552ZC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -12906,7 +12906,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STM32L552RE</t>
+          <t>STM32L552ZC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -12928,12 +12928,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>STM32L562ZE</t>
+          <t>STM32L552ZC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -12943,19 +12943,19 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Table 16. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 27. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>STM32L562ZE</t>
+          <t>STM32L552RE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -12965,19 +12965,19 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Table 16. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 16. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STM32L552ZE</t>
+          <t>STM32L552RE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -12994,12 +12994,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>STM32L552ZE</t>
+          <t>STM32L552RE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -13009,14 +13009,14 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Table 16. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 27. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>STM32L562ME</t>
+          <t>STM32L562ZE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -13038,7 +13038,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>STM32L562ME</t>
+          <t>STM32L562ZE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -13060,12 +13060,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>STM32L552ME</t>
+          <t>STM32L562ZE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -13075,19 +13075,19 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Table 16. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 27. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>STM32L552ME</t>
+          <t>STM32L552ZE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -13104,12 +13104,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>STM32L552VC</t>
+          <t>STM32L552ZE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -13126,12 +13126,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>STM32L552VC</t>
+          <t>STM32L552ZE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -13141,14 +13141,14 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Table 16. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 27. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>STM32L552CC</t>
+          <t>STM32L562ME</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -13163,14 +13163,14 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Table 16. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 16. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>STM32L552CC</t>
+          <t>STM32L562ME</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -13185,19 +13185,19 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Table 16. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 16. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>STM32L562VE</t>
+          <t>STM32L562ME</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -13207,19 +13207,19 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Table 16. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 27. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>STM32L562VE</t>
+          <t>STM32L552ME</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -13229,19 +13229,19 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Table 16. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 16. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>STM32L552VE</t>
+          <t>STM32L552ME</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -13258,12 +13258,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>STM32L552VE</t>
+          <t>STM32L552ME</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -13273,14 +13273,14 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Table 16. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 27. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>STM32L552CE</t>
+          <t>STM32L552VC</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -13302,7 +13302,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>STM32L552CE</t>
+          <t>STM32L552VC</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -13324,12 +13324,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>STM32L552QC</t>
+          <t>STM32L552VC</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -13339,19 +13339,19 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Table 16. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 27. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>STM32L552QC</t>
+          <t>STM32L552CC</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -13368,12 +13368,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>STM32L552RC</t>
+          <t>STM32L552CC</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -13390,12 +13390,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>STM32L552RC</t>
+          <t>STM32L552CC</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -13405,14 +13405,14 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Table 16. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 27. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>STM32L562QE</t>
+          <t>STM32L562VE</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -13434,7 +13434,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>STM32L562QE</t>
+          <t>STM32L562VE</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -13456,12 +13456,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>STM32L562CE</t>
+          <t>STM32L562VE</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -13471,29 +13471,403 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Table 16. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 27. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>STM32L552VE</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Table 16. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>STM32L552VE</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Table 16. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>STM32L552VE</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Table 27. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>STM32L552CE</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Table 16. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>STM32L552CE</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Table 16. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>STM32L552CE</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Table 27. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>STM32L552QC</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Table 16. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>STM32L552QC</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Table 16. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>STM32L552QC</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Table 27. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>STM32L552RC</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Table 16. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>STM32L552RC</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Table 16. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>STM32L552RC</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Table 27. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>STM32L562QE</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Table 16. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>STM32L562QE</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Table 16. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>STM32L562QE</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Table 27. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
           <t>STM32L562CE</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Table 16. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>STM32L562CE</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
         <is>
           <t>Timers (32-bit) typ</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>Table 16. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>STM32L562CE</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Table 27. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>

--- a/product_selector_out/STM32L5 series.xlsx
+++ b/product_selector_out/STM32L5 series.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM28"/>
+  <dimension ref="A1:BN28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.5390625" customWidth="1" min="1" max="1"/>
@@ -567,7 +567,8 @@
     <col width="21.765625" customWidth="1" min="62" max="62"/>
     <col width="18" customWidth="1" min="63" max="63"/>
     <col width="18" customWidth="1" min="64" max="64"/>
-    <col width="52" customWidth="1" min="65" max="65"/>
+    <col width="18" customWidth="1" min="65" max="65"/>
+    <col width="52" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -895,6 +896,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -990,6 +996,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1314,6 +1321,11 @@
       </c>
       <c r="BM12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l562ce.pdf</t>
         </is>
       </c>
@@ -1641,6 +1653,11 @@
       </c>
       <c r="BM13" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l552cc.pdf</t>
         </is>
       </c>
@@ -1968,6 +1985,11 @@
       </c>
       <c r="BM14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l552cc.pdf</t>
         </is>
       </c>
@@ -2295,6 +2317,11 @@
       </c>
       <c r="BM15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l552cc.pdf</t>
         </is>
       </c>
@@ -2622,6 +2649,11 @@
       </c>
       <c r="BM16" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l562ce.pdf</t>
         </is>
       </c>
@@ -2949,6 +2981,11 @@
       </c>
       <c r="BM17" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l552cc.pdf</t>
         </is>
       </c>
@@ -3276,6 +3313,11 @@
       </c>
       <c r="BM18" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN18" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l562ce.pdf</t>
         </is>
       </c>
@@ -3603,6 +3645,11 @@
       </c>
       <c r="BM19" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN19" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l552cc.pdf</t>
         </is>
       </c>
@@ -3930,6 +3977,11 @@
       </c>
       <c r="BM20" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l552cc.pdf</t>
         </is>
       </c>
@@ -4257,6 +4309,11 @@
       </c>
       <c r="BM21" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN21" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l552cc.pdf</t>
         </is>
       </c>
@@ -4584,6 +4641,11 @@
       </c>
       <c r="BM22" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN22" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l562ce.pdf</t>
         </is>
       </c>
@@ -4911,6 +4973,11 @@
       </c>
       <c r="BM23" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN23" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l552cc.pdf</t>
         </is>
       </c>
@@ -5238,6 +5305,11 @@
       </c>
       <c r="BM24" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN24" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l552cc.pdf</t>
         </is>
       </c>
@@ -5565,6 +5637,11 @@
       </c>
       <c r="BM25" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN25" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l552cc.pdf</t>
         </is>
       </c>
@@ -5892,6 +5969,11 @@
       </c>
       <c r="BM26" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN26" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l552cc.pdf</t>
         </is>
       </c>
@@ -6219,6 +6301,11 @@
       </c>
       <c r="BM27" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN27" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l562ce.pdf</t>
         </is>
       </c>
@@ -6546,12 +6633,17 @@
       </c>
       <c r="BM28" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN28" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l562ce.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="64">
+  <mergeCells count="65">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -6572,16 +6664,14 @@
     <mergeCell ref="BA10:BA11"/>
     <mergeCell ref="BG10:BG11"/>
     <mergeCell ref="Q10:Q11"/>
-    <mergeCell ref="A1:BM8"/>
     <mergeCell ref="AR10:AR11"/>
+    <mergeCell ref="AT10:AT11"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="AT10:AT11"/>
+    <mergeCell ref="BI10:BI11"/>
     <mergeCell ref="AV10:AV11"/>
-    <mergeCell ref="A9:BM9"/>
     <mergeCell ref="BB10:BB11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -6594,6 +6684,7 @@
     <mergeCell ref="AQ10:AQ11"/>
     <mergeCell ref="AW10:AW11"/>
     <mergeCell ref="BH10:BH11"/>
+    <mergeCell ref="BN10:BN11"/>
     <mergeCell ref="AY10:AY11"/>
     <mergeCell ref="BK10:BK11"/>
     <mergeCell ref="A10:A11"/>
@@ -6613,7 +6704,9 @@
     <mergeCell ref="U10:V10"/>
     <mergeCell ref="AG10:AG11"/>
     <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A9:BN9"/>
     <mergeCell ref="H10:H11"/>
+    <mergeCell ref="A1:BN8"/>
     <mergeCell ref="T10:T11"/>
     <mergeCell ref="J10:J11"/>
   </mergeCells>
@@ -6647,7 +6740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM28"/>
+  <dimension ref="A1:BN28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6715,6 +6808,7 @@
     <col width="16" customWidth="1" min="63" max="63"/>
     <col width="16" customWidth="1" min="64" max="64"/>
     <col width="16" customWidth="1" min="65" max="65"/>
+    <col width="16" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7048,6 +7142,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -7143,6 +7242,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -7465,7 +7565,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM12" s="6" t="inlineStr">
+      <c r="BM12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -7792,7 +7897,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM13" s="6" t="inlineStr">
+      <c r="BM13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8119,7 +8229,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM14" s="6" t="inlineStr">
+      <c r="BM14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8446,7 +8561,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM15" s="6" t="inlineStr">
+      <c r="BM15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8773,7 +8893,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM16" s="6" t="inlineStr">
+      <c r="BM16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9100,7 +9225,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM17" s="6" t="inlineStr">
+      <c r="BM17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9427,7 +9557,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM18" s="6" t="inlineStr">
+      <c r="BM18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN18" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9754,7 +9889,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM19" s="6" t="inlineStr">
+      <c r="BM19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN19" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10081,7 +10221,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM20" s="6" t="inlineStr">
+      <c r="BM20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10408,7 +10553,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM21" s="6" t="inlineStr">
+      <c r="BM21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN21" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10735,7 +10885,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM22" s="6" t="inlineStr">
+      <c r="BM22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN22" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11062,7 +11217,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM23" s="6" t="inlineStr">
+      <c r="BM23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN23" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11389,7 +11549,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM24" s="6" t="inlineStr">
+      <c r="BM24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN24" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11716,7 +11881,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM25" s="6" t="inlineStr">
+      <c r="BM25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN25" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12043,7 +12213,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM26" s="6" t="inlineStr">
+      <c r="BM26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN26" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12370,7 +12545,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM27" s="6" t="inlineStr">
+      <c r="BM27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN27" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12697,7 +12877,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM28" s="6" t="inlineStr">
+      <c r="BM28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN28" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12705,8 +12890,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BM9"/>
-    <mergeCell ref="A1:BM8"/>
+    <mergeCell ref="A9:BN9"/>
+    <mergeCell ref="A1:BN8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
